--- a/港岛-渣甸山及黄泥涌峡-皇第/皇第_销控明细表.xlsx
+++ b/港岛-渣甸山及黄泥涌峡-皇第/皇第_销控明细表.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -267,6 +267,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -824,23 +827,19 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -1158,23 +1157,19 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>320000000</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>74714</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1198,7 +1193,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1874,20 +1869,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="D3" s="16" t="n">
+        <v>16</v>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="F3" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1929,12 +1920,12 @@
           <t>19&amp;20</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 5515呎 (3房)
+股权转让
 -
--
-(待售)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -2010,12 +2001,12 @@
         </is>
       </c>
       <c r="B11" s="21" t="inlineStr"/>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 4283呎 (3房)
--
--
-(待售)</t>
+万
+,714/呎
+(23年-08月-14日)</t>
         </is>
       </c>
     </row>
